--- a/output/门店分级与调整建议.xlsx
+++ b/output/门店分级与调整建议.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q43"/>
+  <dimension ref="A1:O43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,60 +444,50 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>营业面积(㎡)</t>
+          <t>营业面积</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>2026H1累计到店销售额(元)</t>
+          <t>2026H1累计到店销售额</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>2026H1累计门店O2O履约贡献(元)</t>
+          <t>2026H1累计门店O2O履约贡献</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>月均到店销售(元)</t>
+          <t>到店坪效(元/㎡/月)</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>月均O2O履约贡献(元)</t>
+          <t>租售比</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>到店坪效(元/㎡/月)</t>
+          <t>面积是否调整</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>租售比</t>
+          <t>分级</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>是否同店口径</t>
+          <t>调整建议</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>分级</t>
+          <t>关键依据</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
-        <is>
-          <t>调整建议</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>关键依据</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
         <is>
           <t>数据状态</t>
         </is>
@@ -526,51 +516,45 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>标准店</t>
+          <t>社区店</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>188</v>
+        <v>135</v>
       </c>
       <c r="G2" t="n">
-        <v>1936424.82</v>
+        <v>1924251.63</v>
       </c>
       <c r="H2" t="n">
-        <v>334049.08</v>
+        <v>78627.08</v>
       </c>
       <c r="I2" t="n">
-        <v>322737.47</v>
+        <v>2376</v>
       </c>
       <c r="J2" t="n">
-        <v>55674.85</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1716.69</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.06</v>
+        <v>0.1532</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>保留</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(1,924,251.63元);门店费用.租金及物业费(月均49,129.68元);门店基础信息.营业面积(135㎡)</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
-        <is>
-          <t>调改:评估降租或优化品类结构</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>到店坪效 1717 元/㎡ ∈ [1000,2000)(C级)</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
         <is>
           <t>已确认</t>
         </is>
@@ -599,51 +583,45 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>标准店</t>
+          <t>社区店</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>370</v>
+        <v>85</v>
       </c>
       <c r="G3" t="n">
-        <v>1959104.68</v>
+        <v>1515757.78</v>
       </c>
       <c r="H3" t="n">
-        <v>255359.24</v>
+        <v>66851.14999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>326517.45</v>
+        <v>2972</v>
       </c>
       <c r="J3" t="n">
-        <v>42559.87</v>
-      </c>
-      <c r="K3" t="n">
-        <v>882.48</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.12</v>
+        <v>0.2161</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>保留</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(1,515,757.78元);门店费用.租金及物业费(月均54,604.87元);门店基础信息.营业面积(85㎡)</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
-        <is>
-          <t>闭店/转前置仓评估</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>到店坪效 882 元/㎡ &lt; 1000(D级触发)</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
         <is>
           <t>已确认</t>
         </is>
@@ -672,51 +650,45 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>前置仓</t>
+          <t>社区店</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>447</v>
+        <v>91</v>
       </c>
       <c r="G4" t="n">
-        <v>4600875.61</v>
+        <v>2882989.64</v>
       </c>
       <c r="H4" t="n">
-        <v>240739.64</v>
+        <v>53981.17</v>
       </c>
       <c r="I4" t="n">
-        <v>766812.6</v>
+        <v>5280</v>
       </c>
       <c r="J4" t="n">
-        <v>40123.27</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1715.46</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.06</v>
+        <v>0.06850000000000001</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>保留并加大投入</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(2,882,989.64元);门店费用.租金及物业费(月均32,891.45元);门店基础信息.营业面积(91㎡)</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
-        <is>
-          <t>调改:评估降租或优化品类结构</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>到店坪效 1715 元/㎡ ∈ [1000,2000)(C级)</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
         <is>
           <t>已确认</t>
         </is>
@@ -745,51 +717,45 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>标准店</t>
+          <t>前置仓</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>241</v>
+        <v>96</v>
       </c>
       <c r="G5" t="n">
-        <v>2076813.95</v>
+        <v>1156191.88</v>
       </c>
       <c r="H5" t="n">
-        <v>304340.04</v>
+        <v>84546.03</v>
       </c>
       <c r="I5" t="n">
-        <v>346135.66</v>
+        <v>2007</v>
       </c>
       <c r="J5" t="n">
-        <v>50723.34</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1436.25</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.13</v>
+        <v>0.165</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>保留</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(1,156,191.88元);门店费用.租金及物业费(月均31,799.51元);门店基础信息.营业面积(96㎡)</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
-        <is>
-          <t>调改:评估降租或优化品类结构</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>到店坪效 1436 元/㎡ ∈ [1000,2000)(C级)</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
         <is>
           <t>已确认</t>
         </is>
@@ -822,47 +788,41 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>188</v>
+        <v>79</v>
       </c>
       <c r="G6" t="n">
-        <v>7991007.68</v>
+        <v>1645163.41</v>
       </c>
       <c r="H6" t="n">
-        <v>212564.59</v>
+        <v>52068.64</v>
       </c>
       <c r="I6" t="n">
-        <v>1331834.61</v>
+        <v>3471</v>
       </c>
       <c r="J6" t="n">
-        <v>35427.43</v>
-      </c>
-      <c r="K6" t="n">
-        <v>7084.23</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.02</v>
+        <v>0.1721</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>保留</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(1,645,163.41元);门店费用.租金及物业费(月均47,184.87元);门店基础信息.营业面积(79㎡)</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
-        <is>
-          <t>保留,加大投入,作为标杆</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>指标正常</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
         <is>
           <t>已确认</t>
         </is>
@@ -891,53 +851,47 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>社区店</t>
+          <t>前置仓</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>415</v>
+        <v>81</v>
       </c>
       <c r="G7" t="n">
-        <v>2257685</v>
+        <v>1847603.58</v>
       </c>
       <c r="H7" t="n">
-        <v>291290.58</v>
+        <v>77140.8</v>
       </c>
       <c r="I7" t="n">
-        <v>376280.83</v>
+        <v>3802</v>
       </c>
       <c r="J7" t="n">
-        <v>48548.43</v>
-      </c>
-      <c r="K7" t="n">
-        <v>906.7</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.12</v>
+        <v>0.0844</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>保留</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(1,847,603.58元);门店费用.租金及物业费(月均25,993.13元);门店基础信息.营业面积(81㎡)</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>排除(面积已调整,不计入同店)</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>到店坪效 907 元/㎡ &lt; 1000(D级触发)</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>已确认</t>
+          <t>待补</t>
         </is>
       </c>
     </row>
@@ -964,51 +918,45 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>前置仓</t>
+          <t>社区店</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>335</v>
+        <v>131</v>
       </c>
       <c r="G8" t="n">
-        <v>3079495.59</v>
+        <v>1901982.59</v>
       </c>
       <c r="H8" t="n">
-        <v>226183.88</v>
+        <v>83719.19</v>
       </c>
       <c r="I8" t="n">
-        <v>513249.26</v>
+        <v>2420</v>
       </c>
       <c r="J8" t="n">
-        <v>37697.31</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1532.09</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.06</v>
+        <v>0.1357</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>保留</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(1,901,982.59元);门店费用.租金及物业费(月均43,002.42元);门店基础信息.营业面积(131㎡)</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
-        <is>
-          <t>调改:评估降租或优化品类结构</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>到店坪效 1532 元/㎡ ∈ [1000,2000)(C级)</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
         <is>
           <t>已确认</t>
         </is>
@@ -1037,51 +985,45 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>社区店</t>
+          <t>旗舰店</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>282</v>
+        <v>77</v>
       </c>
       <c r="G9" t="n">
-        <v>1977662.81</v>
+        <v>2742693.84</v>
       </c>
       <c r="H9" t="n">
-        <v>267758.26</v>
+        <v>96243.52</v>
       </c>
       <c r="I9" t="n">
-        <v>329610.47</v>
+        <v>5937</v>
       </c>
       <c r="J9" t="n">
-        <v>44626.38</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1168.83</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.11</v>
+        <v>0.0854</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>保留并加大投入</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(2,742,693.84元);门店费用.租金及物业费(月均39,029.33元);门店基础信息.营业面积(77㎡)</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
-        <is>
-          <t>调改:评估降租或优化品类结构</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>到店坪效 1169 元/㎡ ∈ [1000,2000)(C级)</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
         <is>
           <t>已确认</t>
         </is>
@@ -1110,51 +1052,45 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>旗舰店</t>
+          <t>前置仓</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>409</v>
+        <v>100</v>
       </c>
       <c r="G10" t="n">
-        <v>6652413.75</v>
+        <v>1940174.49</v>
       </c>
       <c r="H10" t="n">
-        <v>248834.04</v>
+        <v>78954.92</v>
       </c>
       <c r="I10" t="n">
-        <v>1108735.62</v>
+        <v>3234</v>
       </c>
       <c r="J10" t="n">
-        <v>41472.34</v>
-      </c>
-      <c r="K10" t="n">
-        <v>2710.85</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06370000000000001</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>保留</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(1,940,174.49元);门店费用.租金及物业费(月均20,598.83元);门店基础信息.营业面积(100㎡)</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
-        <is>
-          <t>保留,观察改善</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>指标正常</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
         <is>
           <t>已确认</t>
         </is>
@@ -1183,51 +1119,45 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>前置仓</t>
+          <t>社区店</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>314</v>
+        <v>145</v>
       </c>
       <c r="G11" t="n">
-        <v>2580387.42</v>
+        <v>1886338.69</v>
       </c>
       <c r="H11" t="n">
-        <v>273496.47</v>
+        <v>67619.03999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>430064.57</v>
+        <v>2168</v>
       </c>
       <c r="J11" t="n">
-        <v>45582.74</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1369.63</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.12</v>
+        <v>0.2566</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>保留</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(1,886,338.69元);门店费用.租金及物业费(月均80,658.18元);门店基础信息.营业面积(145㎡)</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
-        <is>
-          <t>调改:评估降租或优化品类结构</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>到店坪效 1370 元/㎡ ∈ [1000,2000)(C级)</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
         <is>
           <t>已确认</t>
         </is>
@@ -1256,51 +1186,45 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>社区店</t>
+          <t>标准店</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>153</v>
+        <v>110</v>
       </c>
       <c r="G12" t="n">
-        <v>2785208.04</v>
+        <v>2758310.05</v>
       </c>
       <c r="H12" t="n">
-        <v>214953.91</v>
+        <v>51324</v>
       </c>
       <c r="I12" t="n">
-        <v>464201.34</v>
+        <v>4179</v>
       </c>
       <c r="J12" t="n">
-        <v>35825.65</v>
-      </c>
-      <c r="K12" t="n">
-        <v>3034</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0.05</v>
+        <v>0.0693</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>保留</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(2,758,310.05元);门店费用.租金及物业费(月均31,879.57元);门店基础信息.营业面积(110㎡)</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
-        <is>
-          <t>保留,观察改善</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>指标正常</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
         <is>
           <t>已确认</t>
         </is>
@@ -1329,51 +1253,45 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>社区店</t>
+          <t>前置仓</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>215</v>
+        <v>93</v>
       </c>
       <c r="G13" t="n">
-        <v>1098701.35</v>
+        <v>1104936.58</v>
       </c>
       <c r="H13" t="n">
-        <v>272433.63</v>
+        <v>69809.42</v>
       </c>
       <c r="I13" t="n">
-        <v>183116.89</v>
+        <v>1980</v>
       </c>
       <c r="J13" t="n">
-        <v>45405.6</v>
-      </c>
-      <c r="K13" t="n">
-        <v>851.71</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0.17</v>
+        <v>0.378</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>转前置仓/自提点评估</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(1,104,936.58元);门店费用.租金及物业费(月均69,605.38元);门店基础信息.营业面积(93㎡);租约汇总.租期结束(2028-11-19)</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
-        <is>
-          <t>闭店/转前置仓评估</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>到店坪效 852 元/㎡ &lt; 1000(D级触发)</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
         <is>
           <t>已确认</t>
         </is>
@@ -1402,53 +1320,47 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>旗舰店</t>
+          <t>标准店</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>151</v>
+        <v>185</v>
       </c>
       <c r="G14" t="n">
-        <v>4093174.73</v>
+        <v>2266961.33</v>
       </c>
       <c r="H14" t="n">
-        <v>255157.79</v>
+        <v>56564.06</v>
       </c>
       <c r="I14" t="n">
-        <v>682195.79</v>
+        <v>2042</v>
       </c>
       <c r="J14" t="n">
-        <v>42526.3</v>
-      </c>
-      <c r="K14" t="n">
-        <v>4517.85</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0.04</v>
+        <v>0.2014</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>保留</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(2,266,961.33元);门店费用.租金及物业费(月均76,094.05元);门店基础信息.营业面积(185㎡)</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>排除(面积已调整,不计入同店)</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>指标正常</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>已确认</t>
+          <t>待补</t>
         </is>
       </c>
     </row>
@@ -1475,51 +1387,45 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>前置仓</t>
+          <t>标准店</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>206</v>
+        <v>102</v>
       </c>
       <c r="G15" t="n">
-        <v>1991065.25</v>
+        <v>1830697.87</v>
       </c>
       <c r="H15" t="n">
-        <v>195264.75</v>
+        <v>80164.44</v>
       </c>
       <c r="I15" t="n">
-        <v>331844.21</v>
+        <v>2991</v>
       </c>
       <c r="J15" t="n">
-        <v>32544.12</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1610.89</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0.09</v>
+        <v>0.1004</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>保留</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(1,830,697.87元);门店费用.租金及物业费(月均30,627.04元);门店基础信息.营业面积(102㎡)</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
-        <is>
-          <t>调改:评估降租或优化品类结构</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>到店坪效 1611 元/㎡ ∈ [1000,2000)(C级)</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
         <is>
           <t>已确认</t>
         </is>
@@ -1548,51 +1454,45 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>旗舰店</t>
+          <t>标准店</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>461</v>
+        <v>128</v>
       </c>
       <c r="G16" t="n">
-        <v>10732111.11</v>
+        <v>1898979.1</v>
       </c>
       <c r="H16" t="n">
-        <v>200211.24</v>
+        <v>90963.74000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>1788685.18</v>
+        <v>2473</v>
       </c>
       <c r="J16" t="n">
-        <v>33368.54</v>
-      </c>
-      <c r="K16" t="n">
-        <v>3880.01</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0.03</v>
+        <v>0.0766</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>保留</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(1,898,979.10元);门店费用.租金及物业费(月均24,236.04元);门店基础信息.营业面积(128㎡)</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
-        <is>
-          <t>保留,观察改善</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>指标正常</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
         <is>
           <t>已确认</t>
         </is>
@@ -1621,51 +1521,45 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>前置仓</t>
+          <t>标准店</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>367</v>
+        <v>226</v>
       </c>
       <c r="G17" t="n">
-        <v>4918275.62</v>
+        <v>2205711.72</v>
       </c>
       <c r="H17" t="n">
-        <v>236232.86</v>
+        <v>64647.99</v>
       </c>
       <c r="I17" t="n">
-        <v>819712.6</v>
+        <v>1627</v>
       </c>
       <c r="J17" t="n">
-        <v>39372.14</v>
-      </c>
-      <c r="K17" t="n">
-        <v>2233.55</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.2847</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>调改(降租谈判/品类优化)</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(2,205,711.72元);门店费用.租金及物业费(月均104,656.76元);门店基础信息.营业面积(226㎡)</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
-        <is>
-          <t>保留,观察改善</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>指标正常</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
         <is>
           <t>已确认</t>
         </is>
@@ -1694,51 +1588,45 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>前置仓</t>
+          <t>社区店</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>355</v>
+        <v>102</v>
       </c>
       <c r="G18" t="n">
-        <v>3447546.69</v>
+        <v>794338.79</v>
       </c>
       <c r="H18" t="n">
-        <v>291026.11</v>
+        <v>66870.28</v>
       </c>
       <c r="I18" t="n">
-        <v>574591.12</v>
+        <v>1298</v>
       </c>
       <c r="J18" t="n">
-        <v>48504.35</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1618.57</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0.06</v>
+        <v>0.4344</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>关停(启动闭店评估)</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(794,338.79元);门店费用.租金及物业费(月均57,515.15元);门店基础信息.营业面积(102㎡);租约汇总.租期结束(2026-11-17)</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
-        <is>
-          <t>调改:评估降租或优化品类结构</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>到店坪效 1619 元/㎡ ∈ [1000,2000)(C级)</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
         <is>
           <t>已确认</t>
         </is>
@@ -1767,51 +1655,45 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>标准店</t>
+          <t>社区店</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>214</v>
+        <v>111</v>
       </c>
       <c r="G19" t="n">
-        <v>862724.66</v>
+        <v>3084297.99</v>
       </c>
       <c r="H19" t="n">
-        <v>202117.65</v>
+        <v>76129.7</v>
       </c>
       <c r="I19" t="n">
-        <v>143787.44</v>
+        <v>4631</v>
       </c>
       <c r="J19" t="n">
-        <v>33686.28</v>
-      </c>
-      <c r="K19" t="n">
-        <v>671.9</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0.19</v>
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>保留</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(3,084,297.99元);门店费用.租金及物业费(月均43,202.64元);门店基础信息.营业面积(111㎡)</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
-        <is>
-          <t>闭店/转前置仓评估</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>到店坪效 672 元/㎡ &lt; 1000(D级触发)</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
         <is>
           <t>已确认</t>
         </is>
@@ -1840,51 +1722,45 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>社区店</t>
+          <t>前置仓</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>462</v>
+        <v>94</v>
       </c>
       <c r="G20" t="n">
-        <v>5530431.33</v>
+        <v>1903674.85</v>
       </c>
       <c r="H20" t="n">
-        <v>249221.87</v>
+        <v>48399.38</v>
       </c>
       <c r="I20" t="n">
-        <v>921738.5600000001</v>
+        <v>3375</v>
       </c>
       <c r="J20" t="n">
-        <v>41536.98</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1995.11</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0.06</v>
+        <v>0.08260000000000001</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>保留</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(1,903,674.85元);门店费用.租金及物业费(月均26,204.06元);门店基础信息.营业面积(94㎡)</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
-        <is>
-          <t>调改:评估降租或优化品类结构</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>到店坪效 1995 元/㎡ ∈ [1000,2000)(C级)</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
         <is>
           <t>已确认</t>
         </is>
@@ -1913,51 +1789,45 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>社区店</t>
+          <t>前置仓</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>379</v>
+        <v>136</v>
       </c>
       <c r="G21" t="n">
-        <v>4946691.11</v>
+        <v>2033382.15</v>
       </c>
       <c r="H21" t="n">
-        <v>293422.75</v>
+        <v>60826.62</v>
       </c>
       <c r="I21" t="n">
-        <v>824448.52</v>
+        <v>2492</v>
       </c>
       <c r="J21" t="n">
-        <v>48903.79</v>
-      </c>
-      <c r="K21" t="n">
-        <v>2175.33</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.3125</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>保留</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(2,033,382.15元);门店费用.租金及物业费(月均105,914.52元);门店基础信息.营业面积(136㎡)</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
-        <is>
-          <t>保留,观察改善</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>指标正常</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
         <is>
           <t>已确认</t>
         </is>
@@ -1986,51 +1856,45 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>标准店</t>
+          <t>前置仓</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>299</v>
+        <v>81</v>
       </c>
       <c r="G22" t="n">
-        <v>776848.66</v>
+        <v>1140641.96</v>
       </c>
       <c r="H22" t="n">
-        <v>279506.84</v>
+        <v>58958.44</v>
       </c>
       <c r="I22" t="n">
-        <v>129474.78</v>
+        <v>2347</v>
       </c>
       <c r="J22" t="n">
-        <v>46584.47</v>
-      </c>
-      <c r="K22" t="n">
-        <v>433.03</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0.3</v>
+        <v>0.0979</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>保留</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(1,140,641.96元);门店费用.租金及物业费(月均18,604.30元);门店基础信息.营业面积(81㎡)</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
-        <is>
-          <t>闭店/转前置仓评估</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>到店坪效 433 元/㎡ &lt; 1000(D级触发); 租售比 30.4% ∈ (25%,35%](C级)</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
         <is>
           <t>已确认</t>
         </is>
@@ -2059,51 +1923,45 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>旗舰店</t>
+          <t>社区店</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>378</v>
+        <v>74</v>
       </c>
       <c r="G23" t="n">
-        <v>3070453.45</v>
+        <v>1624796.09</v>
       </c>
       <c r="H23" t="n">
-        <v>259096.75</v>
+        <v>31070.8</v>
       </c>
       <c r="I23" t="n">
-        <v>511742.24</v>
+        <v>3659</v>
       </c>
       <c r="J23" t="n">
-        <v>43182.79</v>
-      </c>
-      <c r="K23" t="n">
-        <v>1353.82</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0.13</v>
+        <v>0.2055</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>保留</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(1,624,796.09元);门店费用.租金及物业费(月均55,636.63元);门店基础信息.营业面积(74㎡)</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
-        <is>
-          <t>调改:评估降租或优化品类结构</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>到店坪效 1354 元/㎡ ∈ [1000,2000)(C级)</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
         <is>
           <t>已确认</t>
         </is>
@@ -2132,51 +1990,45 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>标准店</t>
+          <t>前置仓</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>284</v>
+        <v>129</v>
       </c>
       <c r="G24" t="n">
-        <v>4239210.28</v>
+        <v>636656.67</v>
       </c>
       <c r="H24" t="n">
-        <v>280612.63</v>
+        <v>43369.17</v>
       </c>
       <c r="I24" t="n">
-        <v>706535.05</v>
+        <v>823</v>
       </c>
       <c r="J24" t="n">
-        <v>46768.77</v>
-      </c>
-      <c r="K24" t="n">
-        <v>2487.8</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0.04</v>
+        <v>0.648</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>转前置仓/自提点评估</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(636,656.67元);门店费用.租金及物业费(月均68,755.97元);门店基础信息.营业面积(129㎡);租约汇总.租期结束(2027-04-26)</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
-        <is>
-          <t>保留,观察改善</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>指标正常</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
         <is>
           <t>已确认</t>
         </is>
@@ -2205,51 +2057,45 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>社区店</t>
+          <t>标准店</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>265</v>
+        <v>111</v>
       </c>
       <c r="G25" t="n">
-        <v>3771378.58</v>
+        <v>1969342</v>
       </c>
       <c r="H25" t="n">
-        <v>251097.58</v>
+        <v>96786.60000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>628563.1</v>
+        <v>2957</v>
       </c>
       <c r="J25" t="n">
-        <v>41849.6</v>
-      </c>
-      <c r="K25" t="n">
-        <v>2371.94</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0.08</v>
+        <v>0.1742</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>保留</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(1,969,342.00元);门店费用.租金及物业费(月均57,185.16元);门店基础信息.营业面积(111㎡)</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
-        <is>
-          <t>保留,观察改善</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>指标正常</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
         <is>
           <t>已确认</t>
         </is>
@@ -2282,47 +2128,41 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>192</v>
+        <v>72</v>
       </c>
       <c r="G26" t="n">
-        <v>2118351.51</v>
+        <v>1155707.98</v>
       </c>
       <c r="H26" t="n">
-        <v>285889.79</v>
+        <v>71862.19</v>
       </c>
       <c r="I26" t="n">
-        <v>353058.58</v>
+        <v>2675</v>
       </c>
       <c r="J26" t="n">
-        <v>47648.3</v>
-      </c>
-      <c r="K26" t="n">
-        <v>1838.85</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0.11</v>
+        <v>0.07149999999999999</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>保留</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(1,155,707.98元);门店费用.租金及物业费(月均13,779.76元);门店基础信息.营业面积(72㎡)</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
-        <is>
-          <t>调改:评估降租或优化品类结构</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>到店坪效 1839 元/㎡ ∈ [1000,2000)(C级)</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
         <is>
           <t>已确认</t>
         </is>
@@ -2351,51 +2191,45 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>标准店</t>
+          <t>前置仓</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>150</v>
+        <v>103</v>
       </c>
       <c r="G27" t="n">
-        <v>3096562.48</v>
+        <v>1174517.18</v>
       </c>
       <c r="H27" t="n">
-        <v>249309.02</v>
+        <v>60226.97</v>
       </c>
       <c r="I27" t="n">
-        <v>516093.75</v>
+        <v>1901</v>
       </c>
       <c r="J27" t="n">
-        <v>41551.5</v>
-      </c>
-      <c r="K27" t="n">
-        <v>3440.62</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0.03</v>
+        <v>0.2433</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>调改(降租谈判/品类优化)</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(1,174,517.18元);门店费用.租金及物业费(月均47,631.45元);门店基础信息.营业面积(103㎡)</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
-        <is>
-          <t>保留,观察改善</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>指标正常</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
         <is>
           <t>已确认</t>
         </is>
@@ -2428,47 +2262,41 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>340</v>
+        <v>102</v>
       </c>
       <c r="G28" t="n">
-        <v>3733231.88</v>
+        <v>2999752.68</v>
       </c>
       <c r="H28" t="n">
-        <v>226849.79</v>
+        <v>59406.21</v>
       </c>
       <c r="I28" t="n">
-        <v>622205.3100000001</v>
+        <v>4902</v>
       </c>
       <c r="J28" t="n">
-        <v>37808.3</v>
-      </c>
-      <c r="K28" t="n">
-        <v>1830.02</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0.11</v>
+        <v>0.1497</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>保留</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(2,999,752.68元);门店费用.租金及物业费(月均74,864.83元);门店基础信息.营业面积(102㎡)</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
-        <is>
-          <t>调改:评估降租或优化品类结构</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>到店坪效 1830 元/㎡ ∈ [1000,2000)(C级)</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
         <is>
           <t>已确认</t>
         </is>
@@ -2497,51 +2325,45 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>标准店</t>
+          <t>前置仓</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>332</v>
+        <v>178</v>
       </c>
       <c r="G29" t="n">
-        <v>3808172.92</v>
+        <v>2126302.43</v>
       </c>
       <c r="H29" t="n">
-        <v>210560.39</v>
+        <v>71408.17999999999</v>
       </c>
       <c r="I29" t="n">
-        <v>634695.49</v>
+        <v>1991</v>
       </c>
       <c r="J29" t="n">
-        <v>35093.4</v>
-      </c>
-      <c r="K29" t="n">
-        <v>1911.73</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0.04</v>
+        <v>0.3682</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>转前置仓/自提点评估</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(2,126,302.43元);门店费用.租金及物业费(月均130,475.79元);门店基础信息.营业面积(178㎡);租约汇总.租期结束(2032-11-25)</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
-        <is>
-          <t>调改:评估降租或优化品类结构</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>到店坪效 1912 元/㎡ ∈ [1000,2000)(C级)</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
         <is>
           <t>已确认</t>
         </is>
@@ -2570,51 +2392,45 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>社区店</t>
+          <t>旗舰店</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>126</v>
+        <v>251</v>
       </c>
       <c r="G30" t="n">
-        <v>3140430.12</v>
+        <v>811660.23</v>
       </c>
       <c r="H30" t="n">
-        <v>266680.42</v>
+        <v>52374.83</v>
       </c>
       <c r="I30" t="n">
-        <v>523405.02</v>
+        <v>539</v>
       </c>
       <c r="J30" t="n">
-        <v>44446.74</v>
-      </c>
-      <c r="K30" t="n">
-        <v>4154.01</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0.04</v>
+        <v>1.3883</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>关停(启动闭店评估)</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(811,660.23元);门店费用.租金及物业费(月均187,804.40元);门店基础信息.营业面积(251㎡);租约汇总.租期结束(2026-09-25)</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
-        <is>
-          <t>保留,观察改善</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>指标正常</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr">
         <is>
           <t>已确认</t>
         </is>
@@ -2643,51 +2459,45 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>标准店</t>
+          <t>前置仓</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>466</v>
+        <v>126</v>
       </c>
       <c r="G31" t="n">
-        <v>8373993.65</v>
+        <v>2083298.29</v>
       </c>
       <c r="H31" t="n">
-        <v>208402.73</v>
+        <v>68588.99000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>1395665.61</v>
+        <v>2756</v>
       </c>
       <c r="J31" t="n">
-        <v>34733.79</v>
-      </c>
-      <c r="K31" t="n">
-        <v>2994.99</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0.03</v>
+        <v>0.09619999999999999</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>保留</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(2,083,298.29元);门店费用.租金及物业费(月均33,392.82元);门店基础信息.营业面积(126㎡)</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
-        <is>
-          <t>保留,观察改善</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>指标正常</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
         <is>
           <t>已确认</t>
         </is>
@@ -2716,53 +2526,47 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>标准店</t>
+          <t>旗舰店</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>104</v>
+        <v>64</v>
       </c>
       <c r="G32" t="n">
-        <v>6659081.39</v>
+        <v>1078094.56</v>
       </c>
       <c r="H32" t="n">
-        <v>281939.56</v>
+        <v>65544.94</v>
       </c>
       <c r="I32" t="n">
-        <v>1109846.9</v>
+        <v>2808</v>
       </c>
       <c r="J32" t="n">
-        <v>46989.93</v>
-      </c>
-      <c r="K32" t="n">
-        <v>10671.6</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0.01</v>
+        <v>0.2724</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>保留</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(1,078,094.56元);门店费用.租金及物业费(月均48,943.72元);门店基础信息.营业面积(64㎡)</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>排除(面积已调整,不计入同店)</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>指标正常</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>已确认</t>
+          <t>待补</t>
         </is>
       </c>
     </row>
@@ -2789,51 +2593,45 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>旗舰店</t>
+          <t>前置仓</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G33" t="n">
-        <v>3030382.12</v>
+        <v>1703269.89</v>
       </c>
       <c r="H33" t="n">
-        <v>299112.34</v>
+        <v>83118.31</v>
       </c>
       <c r="I33" t="n">
-        <v>505063.69</v>
+        <v>2103</v>
       </c>
       <c r="J33" t="n">
-        <v>49852.06</v>
-      </c>
-      <c r="K33" t="n">
-        <v>3713.7</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0.03</v>
+        <v>0.2949</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>保留</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(1,703,269.89元);门店费用.租金及物业费(月均83,719.03元);门店基础信息.营业面积(135㎡)</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
-        <is>
-          <t>保留,观察改善</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>指标正常</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
         <is>
           <t>已确认</t>
         </is>
@@ -2862,51 +2660,45 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>标准店</t>
+          <t>前置仓</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>158</v>
+        <v>198</v>
       </c>
       <c r="G34" t="n">
-        <v>1941990.46</v>
+        <v>2126380.2</v>
       </c>
       <c r="H34" t="n">
-        <v>272934.5</v>
+        <v>51326.26</v>
       </c>
       <c r="I34" t="n">
-        <v>323665.08</v>
+        <v>1790</v>
       </c>
       <c r="J34" t="n">
-        <v>45489.08</v>
-      </c>
-      <c r="K34" t="n">
-        <v>2048.51</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0.09</v>
+        <v>0.4204</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>转前置仓/自提点评估</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(2,126,380.20元);门店费用.租金及物业费(月均148,974.82元);门店基础信息.营业面积(198㎡);租约汇总.租期结束(2027-05-13)</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
-        <is>
-          <t>保留,观察改善</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>指标正常</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
         <is>
           <t>已确认</t>
         </is>
@@ -2939,47 +2731,41 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>401</v>
+        <v>231</v>
       </c>
       <c r="G35" t="n">
-        <v>2443763.01</v>
+        <v>800557.76</v>
       </c>
       <c r="H35" t="n">
-        <v>300279.4</v>
+        <v>96238.83</v>
       </c>
       <c r="I35" t="n">
-        <v>407293.84</v>
+        <v>578</v>
       </c>
       <c r="J35" t="n">
-        <v>50046.57</v>
-      </c>
-      <c r="K35" t="n">
-        <v>1015.7</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0.13</v>
+        <v>1.3227</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>转前置仓/自提点评估</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(800,557.76元);门店费用.租金及物业费(月均176,483.89元);门店基础信息.营业面积(231㎡);租约汇总.租期结束(2028-03-02)</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
-        <is>
-          <t>调改:评估降租或优化品类结构</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>到店坪效 1016 元/㎡ ∈ [1000,2000)(C级)</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
         <is>
           <t>已确认</t>
         </is>
@@ -3008,51 +2794,45 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>旗舰店</t>
+          <t>社区店</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>161</v>
+        <v>70</v>
       </c>
       <c r="G36" t="n">
-        <v>3790324.56</v>
+        <v>1618461.29</v>
       </c>
       <c r="H36" t="n">
-        <v>197075.78</v>
+        <v>54050.26</v>
       </c>
       <c r="I36" t="n">
-        <v>631720.76</v>
+        <v>3853</v>
       </c>
       <c r="J36" t="n">
-        <v>32845.96</v>
-      </c>
-      <c r="K36" t="n">
-        <v>3923.73</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0.03</v>
+        <v>0.056</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>保留</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(1,618,461.29元);门店费用.租金及物业费(月均15,115.03元);门店基础信息.营业面积(70㎡)</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
-        <is>
-          <t>保留,观察改善</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>指标正常</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
         <is>
           <t>已确认</t>
         </is>
@@ -3081,51 +2861,45 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>前置仓</t>
+          <t>旗舰店</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>485</v>
+        <v>103</v>
       </c>
       <c r="G37" t="n">
-        <v>791088.09</v>
+        <v>1206445.09</v>
       </c>
       <c r="H37" t="n">
-        <v>189074.69</v>
+        <v>48370.82</v>
       </c>
       <c r="I37" t="n">
-        <v>131848.01</v>
+        <v>1952</v>
       </c>
       <c r="J37" t="n">
-        <v>31512.45</v>
-      </c>
-      <c r="K37" t="n">
-        <v>271.85</v>
-      </c>
-      <c r="L37" t="n">
-        <v>0.38</v>
+        <v>0.2975</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>调改(降租谈判/品类优化)</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(1,206,445.09元);门店费用.租金及物业费(月均59,815.72元);门店基础信息.营业面积(103㎡)</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
-        <is>
-          <t>闭店/转前置仓评估</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>到店坪效 272 元/㎡ &lt; 1000(D级触发); 租售比 38.2% &gt; 35%(D级触发)</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
         <is>
           <t>已确认</t>
         </is>
@@ -3158,47 +2932,41 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>428</v>
+        <v>129</v>
       </c>
       <c r="G38" t="n">
-        <v>3390230.8</v>
+        <v>2097836.45</v>
       </c>
       <c r="H38" t="n">
-        <v>233624.15</v>
+        <v>61957.67</v>
       </c>
       <c r="I38" t="n">
-        <v>565038.47</v>
+        <v>2710</v>
       </c>
       <c r="J38" t="n">
-        <v>38937.36</v>
-      </c>
-      <c r="K38" t="n">
-        <v>1320.18</v>
-      </c>
-      <c r="L38" t="n">
-        <v>0.14</v>
+        <v>0.2195</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>保留</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(2,097,836.45元);门店费用.租金及物业费(月均76,754.54元);门店基础信息.营业面积(129㎡)</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
-        <is>
-          <t>调改:评估降租或优化品类结构</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>到店坪效 1320 元/㎡ ∈ [1000,2000)(C级)</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr">
         <is>
           <t>已确认</t>
         </is>
@@ -3227,51 +2995,45 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>社区店</t>
+          <t>标准店</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>296</v>
+        <v>76</v>
       </c>
       <c r="G39" t="n">
-        <v>4124565.75</v>
+        <v>1652896.21</v>
       </c>
       <c r="H39" t="n">
-        <v>269851.29</v>
+        <v>90020.12</v>
       </c>
       <c r="I39" t="n">
-        <v>687427.62</v>
+        <v>3625</v>
       </c>
       <c r="J39" t="n">
-        <v>44975.22</v>
-      </c>
-      <c r="K39" t="n">
-        <v>2322.39</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0.05</v>
+        <v>0.1208</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>保留</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(1,652,896.21元);门店费用.租金及物业费(月均33,283.71元);门店基础信息.营业面积(76㎡)</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
-        <is>
-          <t>保留,观察改善</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>指标正常</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr">
         <is>
           <t>已确认</t>
         </is>
@@ -3300,51 +3062,45 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>前置仓</t>
+          <t>标准店</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>385</v>
+        <v>118</v>
       </c>
       <c r="G40" t="n">
-        <v>5878138.39</v>
+        <v>1785056.94</v>
       </c>
       <c r="H40" t="n">
-        <v>328411.69</v>
+        <v>62212.25</v>
       </c>
       <c r="I40" t="n">
-        <v>979689.73</v>
+        <v>2521</v>
       </c>
       <c r="J40" t="n">
-        <v>54735.28</v>
-      </c>
-      <c r="K40" t="n">
-        <v>2544.65</v>
-      </c>
-      <c r="L40" t="n">
-        <v>0.04</v>
+        <v>0.1524</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>保留</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(1,785,056.94元);门店费用.租金及物业费(月均45,354.29元);门店基础信息.营业面积(118㎡)</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
-        <is>
-          <t>保留,观察改善</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>指标正常</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr">
         <is>
           <t>已确认</t>
         </is>
@@ -3373,51 +3129,45 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>社区店</t>
+          <t>旗舰店</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>112</v>
+        <v>84</v>
       </c>
       <c r="G41" t="n">
-        <v>1302625.37</v>
+        <v>1821262.13</v>
       </c>
       <c r="H41" t="n">
-        <v>262529.39</v>
+        <v>89149.58</v>
       </c>
       <c r="I41" t="n">
-        <v>217104.23</v>
+        <v>3614</v>
       </c>
       <c r="J41" t="n">
-        <v>43754.9</v>
-      </c>
-      <c r="K41" t="n">
-        <v>1938.43</v>
-      </c>
-      <c r="L41" t="n">
-        <v>0.08</v>
+        <v>0.0591</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>保留</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(1,821,262.13元);门店费用.租金及物业费(月均17,926.01元);门店基础信息.营业面积(84㎡)</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
-        <is>
-          <t>调改:评估降租或优化品类结构</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>到店坪效 1938 元/㎡ ∈ [1000,2000)(C级)</t>
-        </is>
-      </c>
-      <c r="Q41" t="inlineStr">
         <is>
           <t>已确认</t>
         </is>
@@ -3446,51 +3196,45 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>前置仓</t>
+          <t>标准店</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>277</v>
+        <v>111</v>
       </c>
       <c r="G42" t="n">
-        <v>3935098.13</v>
+        <v>3468905.55</v>
       </c>
       <c r="H42" t="n">
-        <v>286654.94</v>
+        <v>57359.3</v>
       </c>
       <c r="I42" t="n">
-        <v>655849.6899999999</v>
+        <v>5209</v>
       </c>
       <c r="J42" t="n">
-        <v>47775.82</v>
-      </c>
-      <c r="K42" t="n">
-        <v>2367.69</v>
-      </c>
-      <c r="L42" t="n">
-        <v>0.06</v>
+        <v>0.0446</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>保留并加大投入</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(3,468,905.55元);门店费用.租金及物业费(月均25,808.68元);门店基础信息.营业面积(111㎡)</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
-        <is>
-          <t>保留,观察改善</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>指标正常</t>
-        </is>
-      </c>
-      <c r="Q42" t="inlineStr">
         <is>
           <t>已确认</t>
         </is>
@@ -3519,51 +3263,45 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>前置仓</t>
+          <t>标准店</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>275</v>
+        <v>101</v>
       </c>
       <c r="G43" t="n">
-        <v>2126841.95</v>
+        <v>1986525.16</v>
       </c>
       <c r="H43" t="n">
-        <v>258108.46</v>
+        <v>72490.49000000001</v>
       </c>
       <c r="I43" t="n">
-        <v>354473.66</v>
+        <v>3278</v>
       </c>
       <c r="J43" t="n">
-        <v>43018.08</v>
-      </c>
-      <c r="K43" t="n">
-        <v>1289</v>
-      </c>
-      <c r="L43" t="n">
-        <v>0.08</v>
+        <v>0.154</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>保留</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(1,986,525.16元);门店费用.租金及物业费(月均51,003.03元);门店基础信息.营业面积(101㎡)</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
-        <is>
-          <t>调改:评估降租或优化品类结构</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>到店坪效 1289 元/㎡ ∈ [1000,2000)(C级)</t>
-        </is>
-      </c>
-      <c r="Q43" t="inlineStr">
         <is>
           <t>已确认</t>
         </is>

--- a/output/门店分级与调整建议.xlsx
+++ b/output/门店分级与调整建议.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="门店清单" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Check" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,13 +26,21 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +55,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -546,7 +563,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>保留</t>
+          <t>维持</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -613,7 +630,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>保留</t>
+          <t>维持</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -680,7 +697,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>保留并加大投入</t>
+          <t>维持</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -747,7 +764,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>保留</t>
+          <t>维持</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -814,7 +831,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>保留</t>
+          <t>维持</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -881,7 +898,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>保留</t>
+          <t>维持</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -948,7 +965,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>保留</t>
+          <t>维持</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1015,7 +1032,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>保留并加大投入</t>
+          <t>维持</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1082,7 +1099,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>保留</t>
+          <t>维持</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1149,7 +1166,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>保留</t>
+          <t>维持</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1216,7 +1233,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>保留</t>
+          <t>维持</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1283,7 +1300,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>转前置仓/自提点评估</t>
+          <t>转前置仓或自提点</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1350,7 +1367,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>保留</t>
+          <t>维持</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1417,7 +1434,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>保留</t>
+          <t>维持</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1484,7 +1501,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>保留</t>
+          <t>维持</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1551,7 +1568,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>调改(降租谈判/品类优化)</t>
+          <t>整改</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1618,7 +1635,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>关停(启动闭店评估)</t>
+          <t>闭店评估</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1685,7 +1702,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>保留</t>
+          <t>维持</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1752,7 +1769,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>保留</t>
+          <t>维持</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1819,7 +1836,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>保留</t>
+          <t>维持</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1886,7 +1903,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>保留</t>
+          <t>维持</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1953,7 +1970,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>保留</t>
+          <t>维持</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2020,7 +2037,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>转前置仓/自提点评估</t>
+          <t>转前置仓或自提点</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2087,7 +2104,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>保留</t>
+          <t>维持</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2154,7 +2171,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>保留</t>
+          <t>维持</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2221,7 +2238,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>调改(降租谈判/品类优化)</t>
+          <t>整改</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2288,7 +2305,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>保留</t>
+          <t>维持</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2355,7 +2372,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>转前置仓/自提点评估</t>
+          <t>转前置仓或自提点</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2422,7 +2439,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>关停(启动闭店评估)</t>
+          <t>闭店评估</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2489,7 +2506,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>保留</t>
+          <t>维持</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2556,7 +2573,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>保留</t>
+          <t>维持</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2623,7 +2640,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>保留</t>
+          <t>维持</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2690,7 +2707,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>转前置仓/自提点评估</t>
+          <t>转前置仓或自提点</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2757,7 +2774,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>转前置仓/自提点评估</t>
+          <t>转前置仓或自提点</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2824,7 +2841,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>保留</t>
+          <t>维持</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -2891,7 +2908,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>调改(降租谈判/品类优化)</t>
+          <t>整改</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -2958,7 +2975,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>保留</t>
+          <t>维持</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3025,7 +3042,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>保留</t>
+          <t>维持</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3092,7 +3109,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>保留</t>
+          <t>维持</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3159,7 +3176,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>保留</t>
+          <t>维持</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3226,7 +3243,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>保留并加大投入</t>
+          <t>维持</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3293,7 +3310,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>保留</t>
+          <t>维持</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3304,6 +3321,143 @@
       <c r="O43" t="inlineStr">
         <is>
           <t>已确认</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="4">
+    <dataValidation sqref="K2:K43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值超出规定枚举" error="请使用规定枚举值" type="list">
+      <formula1>"是,否"</formula1>
+    </dataValidation>
+    <dataValidation sqref="L2:L43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值超出规定枚举" error="请使用规定枚举值" type="list">
+      <formula1>"A,B,C,D"</formula1>
+    </dataValidation>
+    <dataValidation sqref="M2:M43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值超出规定枚举" error="请使用规定枚举值" type="list">
+      <formula1>"维持,整改,转前置仓或自提点,闭店评估"</formula1>
+    </dataValidation>
+    <dataValidation sqref="O2:O43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值超出规定枚举" error="请使用规定枚举值" type="list">
+      <formula1>"已确认,待补"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>门店清单 自查区(只读;公式由 Excel 计算)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>校验项</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>结果</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>期望/口径</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>对象行数</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>COUNTA('门店清单'!A2:A43)</f>
+        <v/>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>应为 42(全量门店)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>坪效最大差异(元/㎡/月)</t>
+        </is>
+      </c>
+      <c r="B5" s="3">
+        <f>MAX(ABS('门店清单'!I2:I43-ROUND('门店清单'!G2:G43/6/'门店清单'!F2:F43,0)))</f>
+        <v/>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>复算 = 累计到店销售额 ÷ 6 ÷ 营业面积,取整数;应 ≤ 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>分级与坪效/租售比阈值不一致家数</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>SUMPRODUCT(--('门店清单'!L2:L43&lt;&gt;IF('门店清单'!J2:J43&gt;0.35,"D",IF('门店清单'!I2:I43&gt;=5000,"A",IF('门店清单'!I2:I43&gt;=2000,"B",IF('门店清单'!I2:I43&gt;=1000,"C","D")))))</f>
+        <v/>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>分级应 = 坪效定级,且租售比 &gt;35% 直接 D 级;应为 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>面积调整门店未标待补家数</t>
+        </is>
+      </c>
+      <c r="B7" s="3">
+        <f>SUMPRODUCT(--(('门店清单'!K2:K43="是")*('门店清单'!O2:O43&lt;&gt;"待补")))</f>
+        <v/>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>面积调整门店的数据状态应为「待补」;应为 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>枚举违规家数(分级/调整建议/数据状态/面积是否调整)</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>SUMPRODUCT(--(ISNA(MATCH('门店清单'!L2:L43,{"A";"B";"C";"D"},0))))+SUMPRODUCT(--(ISNA(MATCH('门店清单'!M2:M43,{"维持";"整改";"转前置仓或自提点";"闭店评估"},0))))+SUMPRODUCT(--(ISNA(MATCH('门店清单'!O2:O43,{"已确认";"待补"},0))))+SUMPRODUCT(--(ISNA(MATCH('门店清单'!K2:K43,{"是";"否"},0))))</f>
+        <v/>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>四个枚举列取值应落在规定集合内;应为 0</t>
         </is>
       </c>
     </row>

--- a/output/门店分级与调整建议.xlsx
+++ b/output/门店分级与调整建议.xlsx
@@ -3326,16 +3326,16 @@
     </row>
   </sheetData>
   <dataValidations count="4">
-    <dataValidation sqref="K2:K43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值超出规定枚举" error="请使用规定枚举值" type="list">
+    <dataValidation sqref="K2:K200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值超出规定枚举" error="请使用规定枚举值" type="list">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation sqref="L2:L43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值超出规定枚举" error="请使用规定枚举值" type="list">
+    <dataValidation sqref="L2:L200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值超出规定枚举" error="请使用规定枚举值" type="list">
       <formula1>"A,B,C,D"</formula1>
     </dataValidation>
-    <dataValidation sqref="M2:M43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值超出规定枚举" error="请使用规定枚举值" type="list">
+    <dataValidation sqref="M2:M200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值超出规定枚举" error="请使用规定枚举值" type="list">
       <formula1>"维持,整改,转前置仓或自提点,闭店评估"</formula1>
     </dataValidation>
-    <dataValidation sqref="O2:O43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值超出规定枚举" error="请使用规定枚举值" type="list">
+    <dataValidation sqref="O2:O200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值超出规定枚举" error="请使用规定枚举值" type="list">
       <formula1>"已确认,待补"</formula1>
     </dataValidation>
   </dataValidations>

--- a/output/门店分级与调整建议.xlsx
+++ b/output/门店分级与调整建议.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="门店清单" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Check" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,21 +25,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9D9D9"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -55,16 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3325,143 +3308,11 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="4">
-    <dataValidation sqref="K2:K200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值超出规定枚举" error="请使用规定枚举值" type="list">
-      <formula1>"是,否"</formula1>
-    </dataValidation>
-    <dataValidation sqref="L2:L200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值超出规定枚举" error="请使用规定枚举值" type="list">
-      <formula1>"A,B,C,D"</formula1>
-    </dataValidation>
-    <dataValidation sqref="M2:M200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值超出规定枚举" error="请使用规定枚举值" type="list">
-      <formula1>"维持,整改,转前置仓或自提点,闭店评估"</formula1>
-    </dataValidation>
+  <dataValidations count="1">
     <dataValidation sqref="O2:O200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值超出规定枚举" error="请使用规定枚举值" type="list">
       <formula1>"已确认,待补"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>门店清单 自查区(只读;公式由 Excel 计算)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>校验项</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>结果</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>期望/口径</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>对象行数</t>
-        </is>
-      </c>
-      <c r="B4" s="3">
-        <f>COUNTA('门店清单'!A2:A43)</f>
-        <v/>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>应为 42(全量门店)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>坪效最大差异(元/㎡/月)</t>
-        </is>
-      </c>
-      <c r="B5" s="3">
-        <f>MAX(ABS('门店清单'!I2:I43-ROUND('门店清单'!G2:G43/6/'门店清单'!F2:F43,0)))</f>
-        <v/>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>复算 = 累计到店销售额 ÷ 6 ÷ 营业面积,取整数;应 ≤ 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>分级与坪效/租售比阈值不一致家数</t>
-        </is>
-      </c>
-      <c r="B6" s="3">
-        <f>SUMPRODUCT(--('门店清单'!L2:L43&lt;&gt;IF('门店清单'!J2:J43&gt;0.35,"D",IF('门店清单'!I2:I43&gt;=5000,"A",IF('门店清单'!I2:I43&gt;=2000,"B",IF('门店清单'!I2:I43&gt;=1000,"C","D")))))</f>
-        <v/>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>分级应 = 坪效定级,且租售比 &gt;35% 直接 D 级;应为 0</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>面积调整门店未标待补家数</t>
-        </is>
-      </c>
-      <c r="B7" s="3">
-        <f>SUMPRODUCT(--(('门店清单'!K2:K43="是")*('门店清单'!O2:O43&lt;&gt;"待补")))</f>
-        <v/>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>面积调整门店的数据状态应为「待补」;应为 0</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>枚举违规家数(分级/调整建议/数据状态/面积是否调整)</t>
-        </is>
-      </c>
-      <c r="B8" s="3">
-        <f>SUMPRODUCT(--(ISNA(MATCH('门店清单'!L2:L43,{"A";"B";"C";"D"},0))))+SUMPRODUCT(--(ISNA(MATCH('门店清单'!M2:M43,{"维持";"整改";"转前置仓或自提点";"闭店评估"},0))))+SUMPRODUCT(--(ISNA(MATCH('门店清单'!O2:O43,{"已确认";"待补"},0))))+SUMPRODUCT(--(ISNA(MATCH('门店清单'!K2:K43,{"是";"否"},0))))</f>
-        <v/>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>四个枚举列取值应落在规定集合内;应为 0</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/output/门店分级与调整建议.xlsx
+++ b/output/门店分级与调整建议.xlsx
@@ -449,17 +449,17 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>2026H1累计到店销售额</t>
+          <t>2026H1 累计到店销售额</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>2026H1累计门店O2O履约贡献</t>
+          <t>2026H1 累计门店 O2O 履约贡献</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>到店坪效(元/㎡/月)</t>
+          <t>到店坪效</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -474,22 +474,22 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>分级</t>
+          <t>分级(A/B/C/D)</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>调整建议</t>
+          <t>调整建议(维持/整改/转前置仓或自提点/闭店评估)</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>关键依据</t>
+          <t>关键依据(2–3 条材料引用)</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>数据状态</t>
+          <t>数据状态(已确认/待补)</t>
         </is>
       </c>
     </row>
@@ -551,7 +551,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(1,924,251.63元);门店费用.租金及物业费(月均49,129.68元);门店基础信息.营业面积(135㎡)</t>
+          <t>《2026H1门店经营台账.xlsx》Sheet「门店月度经营」的 `到店销售额`(2026H1 累计 1,924,251.63 元);《2026H1门店经营台账.xlsx》Sheet「门店费用」的 `租金及物业费`(月均 49,129.68 元);《2026H1门店经营台账.xlsx》Sheet「门店基础信息」的 `营业面积`(135 ㎡)</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(1,515,757.78元);门店费用.租金及物业费(月均54,604.87元);门店基础信息.营业面积(85㎡)</t>
+          <t>《2026H1门店经营台账.xlsx》Sheet「门店月度经营」的 `到店销售额`(2026H1 累计 1,515,757.78 元);《2026H1门店经营台账.xlsx》Sheet「门店费用」的 `租金及物业费`(月均 54,604.87 元);《2026H1门店经营台账.xlsx》Sheet「门店基础信息」的 `营业面积`(85 ㎡)</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(2,882,989.64元);门店费用.租金及物业费(月均32,891.45元);门店基础信息.营业面积(91㎡)</t>
+          <t>《2026H1门店经营台账.xlsx》Sheet「门店月度经营」的 `到店销售额`(2026H1 累计 2,882,989.64 元);《2026H1门店经营台账.xlsx》Sheet「门店费用」的 `租金及物业费`(月均 32,891.45 元);《2026H1门店经营台账.xlsx》Sheet「门店基础信息」的 `营业面积`(91 ㎡)</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(1,156,191.88元);门店费用.租金及物业费(月均31,799.51元);门店基础信息.营业面积(96㎡)</t>
+          <t>《2026H1门店经营台账.xlsx》Sheet「门店月度经营」的 `到店销售额`(2026H1 累计 1,156,191.88 元);《2026H1门店经营台账.xlsx》Sheet「门店费用」的 `租金及物业费`(月均 31,799.51 元);《2026H1门店经营台账.xlsx》Sheet「门店基础信息」的 `营业面积`(96 ㎡)</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(1,645,163.41元);门店费用.租金及物业费(月均47,184.87元);门店基础信息.营业面积(79㎡)</t>
+          <t>《2026H1门店经营台账.xlsx》Sheet「门店月度经营」的 `到店销售额`(2026H1 累计 1,645,163.41 元);《2026H1门店经营台账.xlsx》Sheet「门店费用」的 `租金及物业费`(月均 47,184.87 元);《2026H1门店经营台账.xlsx》Sheet「门店基础信息」的 `营业面积`(79 ㎡)</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(1,847,603.58元);门店费用.租金及物业费(月均25,993.13元);门店基础信息.营业面积(81㎡)</t>
+          <t>《2026H1门店经营台账.xlsx》Sheet「门店月度经营」的 `到店销售额`(2026H1 累计 1,847,603.58 元);《2026H1门店经营台账.xlsx》Sheet「门店费用」的 `租金及物业费`(月均 25,993.13 元);《2026H1门店经营台账.xlsx》Sheet「门店基础信息」的 `营业面积`(81 ㎡)</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(1,901,982.59元);门店费用.租金及物业费(月均43,002.42元);门店基础信息.营业面积(131㎡)</t>
+          <t>《2026H1门店经营台账.xlsx》Sheet「门店月度经营」的 `到店销售额`(2026H1 累计 1,901,982.59 元);《2026H1门店经营台账.xlsx》Sheet「门店费用」的 `租金及物业费`(月均 43,002.42 元);《2026H1门店经营台账.xlsx》Sheet「门店基础信息」的 `营业面积`(131 ㎡)</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(2,742,693.84元);门店费用.租金及物业费(月均39,029.33元);门店基础信息.营业面积(77㎡)</t>
+          <t>《2026H1门店经营台账.xlsx》Sheet「门店月度经营」的 `到店销售额`(2026H1 累计 2,742,693.84 元);《2026H1门店经营台账.xlsx》Sheet「门店费用」的 `租金及物业费`(月均 39,029.33 元);《2026H1门店经营台账.xlsx》Sheet「门店基础信息」的 `营业面积`(77 ㎡)</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(1,940,174.49元);门店费用.租金及物业费(月均20,598.83元);门店基础信息.营业面积(100㎡)</t>
+          <t>《2026H1门店经营台账.xlsx》Sheet「门店月度经营」的 `到店销售额`(2026H1 累计 1,940,174.49 元);《2026H1门店经营台账.xlsx》Sheet「门店费用」的 `租金及物业费`(月均 20,598.83 元);《2026H1门店经营台账.xlsx》Sheet「门店基础信息」的 `营业面积`(100 ㎡)</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(1,886,338.69元);门店费用.租金及物业费(月均80,658.18元);门店基础信息.营业面积(145㎡)</t>
+          <t>《2026H1门店经营台账.xlsx》Sheet「门店月度经营」的 `到店销售额`(2026H1 累计 1,886,338.69 元);《2026H1门店经营台账.xlsx》Sheet「门店费用」的 `租金及物业费`(月均 80,658.18 元);《2026H1门店经营台账.xlsx》Sheet「门店基础信息」的 `营业面积`(145 ㎡)</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(2,758,310.05元);门店费用.租金及物业费(月均31,879.57元);门店基础信息.营业面积(110㎡)</t>
+          <t>《2026H1门店经营台账.xlsx》Sheet「门店月度经营」的 `到店销售额`(2026H1 累计 2,758,310.05 元);《2026H1门店经营台账.xlsx》Sheet「门店费用」的 `租金及物业费`(月均 31,879.57 元);《2026H1门店经营台账.xlsx》Sheet「门店基础信息」的 `营业面积`(110 ㎡)</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(1,104,936.58元);门店费用.租金及物业费(月均69,605.38元);门店基础信息.营业面积(93㎡);租约汇总.租期结束(2028-11-19)</t>
+          <t>《2026H1门店经营台账.xlsx》Sheet「门店月度经营」的 `到店销售额`(2026H1 累计 1,104,936.58 元);《2026H1门店经营台账.xlsx》Sheet「门店费用」的 `租金及物业费`(月均 69,605.38 元);《2026H1门店经营台账.xlsx》Sheet「门店基础信息」的 `营业面积`(93 ㎡);《华东区门店租约汇总.docx》该门店的 `租期结束`(2028-11-19)与 `闭店条件`</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(2,266,961.33元);门店费用.租金及物业费(月均76,094.05元);门店基础信息.营业面积(185㎡)</t>
+          <t>《2026H1门店经营台账.xlsx》Sheet「门店月度经营」的 `到店销售额`(2026H1 累计 2,266,961.33 元);《2026H1门店经营台账.xlsx》Sheet「门店费用」的 `租金及物业费`(月均 76,094.05 元);《2026H1门店经营台账.xlsx》Sheet「门店基础信息」的 `营业面积`(185 ㎡)</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(1,830,697.87元);门店费用.租金及物业费(月均30,627.04元);门店基础信息.营业面积(102㎡)</t>
+          <t>《2026H1门店经营台账.xlsx》Sheet「门店月度经营」的 `到店销售额`(2026H1 累计 1,830,697.87 元);《2026H1门店经营台账.xlsx》Sheet「门店费用」的 `租金及物业费`(月均 30,627.04 元);《2026H1门店经营台账.xlsx》Sheet「门店基础信息」的 `营业面积`(102 ㎡)</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(1,898,979.10元);门店费用.租金及物业费(月均24,236.04元);门店基础信息.营业面积(128㎡)</t>
+          <t>《2026H1门店经营台账.xlsx》Sheet「门店月度经营」的 `到店销售额`(2026H1 累计 1,898,979.10 元);《2026H1门店经营台账.xlsx》Sheet「门店费用」的 `租金及物业费`(月均 24,236.04 元);《2026H1门店经营台账.xlsx》Sheet「门店基础信息」的 `营业面积`(128 ㎡)</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(2,205,711.72元);门店费用.租金及物业费(月均104,656.76元);门店基础信息.营业面积(226㎡)</t>
+          <t>《2026H1门店经营台账.xlsx》Sheet「门店月度经营」的 `到店销售额`(2026H1 累计 2,205,711.72 元);《2026H1门店经营台账.xlsx》Sheet「门店费用」的 `租金及物业费`(月均 104,656.76 元);《2026H1门店经营台账.xlsx》Sheet「门店基础信息」的 `营业面积`(226 ㎡)</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(794,338.79元);门店费用.租金及物业费(月均57,515.15元);门店基础信息.营业面积(102㎡);租约汇总.租期结束(2026-11-17)</t>
+          <t>《2026H1门店经营台账.xlsx》Sheet「门店月度经营」的 `到店销售额`(2026H1 累计 794,338.79 元);《2026H1门店经营台账.xlsx》Sheet「门店费用」的 `租金及物业费`(月均 57,515.15 元);《2026H1门店经营台账.xlsx》Sheet「门店基础信息」的 `营业面积`(102 ㎡);《华东区门店租约汇总.docx》该门店的 `租期结束`(2026-11-17)与 `闭店条件`</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(3,084,297.99元);门店费用.租金及物业费(月均43,202.64元);门店基础信息.营业面积(111㎡)</t>
+          <t>《2026H1门店经营台账.xlsx》Sheet「门店月度经营」的 `到店销售额`(2026H1 累计 3,084,297.99 元);《2026H1门店经营台账.xlsx》Sheet「门店费用」的 `租金及物业费`(月均 43,202.64 元);《2026H1门店经营台账.xlsx》Sheet「门店基础信息」的 `营业面积`(111 ㎡)</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(1,903,674.85元);门店费用.租金及物业费(月均26,204.06元);门店基础信息.营业面积(94㎡)</t>
+          <t>《2026H1门店经营台账.xlsx》Sheet「门店月度经营」的 `到店销售额`(2026H1 累计 1,903,674.85 元);《2026H1门店经营台账.xlsx》Sheet「门店费用」的 `租金及物业费`(月均 26,204.06 元);《2026H1门店经营台账.xlsx》Sheet「门店基础信息」的 `营业面积`(94 ㎡)</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(2,033,382.15元);门店费用.租金及物业费(月均105,914.52元);门店基础信息.营业面积(136㎡)</t>
+          <t>《2026H1门店经营台账.xlsx》Sheet「门店月度经营」的 `到店销售额`(2026H1 累计 2,033,382.15 元);《2026H1门店经营台账.xlsx》Sheet「门店费用」的 `租金及物业费`(月均 105,914.52 元);《2026H1门店经营台账.xlsx》Sheet「门店基础信息」的 `营业面积`(136 ㎡)</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(1,140,641.96元);门店费用.租金及物业费(月均18,604.30元);门店基础信息.营业面积(81㎡)</t>
+          <t>《2026H1门店经营台账.xlsx》Sheet「门店月度经营」的 `到店销售额`(2026H1 累计 1,140,641.96 元);《2026H1门店经营台账.xlsx》Sheet「门店费用」的 `租金及物业费`(月均 18,604.30 元);《2026H1门店经营台账.xlsx》Sheet「门店基础信息」的 `营业面积`(81 ㎡)</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(1,624,796.09元);门店费用.租金及物业费(月均55,636.63元);门店基础信息.营业面积(74㎡)</t>
+          <t>《2026H1门店经营台账.xlsx》Sheet「门店月度经营」的 `到店销售额`(2026H1 累计 1,624,796.09 元);《2026H1门店经营台账.xlsx》Sheet「门店费用」的 `租金及物业费`(月均 55,636.63 元);《2026H1门店经营台账.xlsx》Sheet「门店基础信息」的 `营业面积`(74 ㎡)</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(636,656.67元);门店费用.租金及物业费(月均68,755.97元);门店基础信息.营业面积(129㎡);租约汇总.租期结束(2027-04-26)</t>
+          <t>《2026H1门店经营台账.xlsx》Sheet「门店月度经营」的 `到店销售额`(2026H1 累计 636,656.67 元);《2026H1门店经营台账.xlsx》Sheet「门店费用」的 `租金及物业费`(月均 68,755.97 元);《2026H1门店经营台账.xlsx》Sheet「门店基础信息」的 `营业面积`(129 ㎡);《华东区门店租约汇总.docx》该门店的 `租期结束`(2027-04-26)与 `闭店条件`</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2092,7 +2092,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(1,969,342.00元);门店费用.租金及物业费(月均57,185.16元);门店基础信息.营业面积(111㎡)</t>
+          <t>《2026H1门店经营台账.xlsx》Sheet「门店月度经营」的 `到店销售额`(2026H1 累计 1,969,342.00 元);《2026H1门店经营台账.xlsx》Sheet「门店费用」的 `租金及物业费`(月均 57,185.16 元);《2026H1门店经营台账.xlsx》Sheet「门店基础信息」的 `营业面积`(111 ㎡)</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(1,155,707.98元);门店费用.租金及物业费(月均13,779.76元);门店基础信息.营业面积(72㎡)</t>
+          <t>《2026H1门店经营台账.xlsx》Sheet「门店月度经营」的 `到店销售额`(2026H1 累计 1,155,707.98 元);《2026H1门店经营台账.xlsx》Sheet「门店费用」的 `租金及物业费`(月均 13,779.76 元);《2026H1门店经营台账.xlsx》Sheet「门店基础信息」的 `营业面积`(72 ㎡)</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(1,174,517.18元);门店费用.租金及物业费(月均47,631.45元);门店基础信息.营业面积(103㎡)</t>
+          <t>《2026H1门店经营台账.xlsx》Sheet「门店月度经营」的 `到店销售额`(2026H1 累计 1,174,517.18 元);《2026H1门店经营台账.xlsx》Sheet「门店费用」的 `租金及物业费`(月均 47,631.45 元);《2026H1门店经营台账.xlsx》Sheet「门店基础信息」的 `营业面积`(103 ㎡)</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(2,999,752.68元);门店费用.租金及物业费(月均74,864.83元);门店基础信息.营业面积(102㎡)</t>
+          <t>《2026H1门店经营台账.xlsx》Sheet「门店月度经营」的 `到店销售额`(2026H1 累计 2,999,752.68 元);《2026H1门店经营台账.xlsx》Sheet「门店费用」的 `租金及物业费`(月均 74,864.83 元);《2026H1门店经营台账.xlsx》Sheet「门店基础信息」的 `营业面积`(102 ㎡)</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(2,126,302.43元);门店费用.租金及物业费(月均130,475.79元);门店基础信息.营业面积(178㎡);租约汇总.租期结束(2032-11-25)</t>
+          <t>《2026H1门店经营台账.xlsx》Sheet「门店月度经营」的 `到店销售额`(2026H1 累计 2,126,302.43 元);《2026H1门店经营台账.xlsx》Sheet「门店费用」的 `租金及物业费`(月均 130,475.79 元);《2026H1门店经营台账.xlsx》Sheet「门店基础信息」的 `营业面积`(178 ㎡);《华东区门店租约汇总.docx》该门店的 `租期结束`(2032-11-25)与 `闭店条件`</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(811,660.23元);门店费用.租金及物业费(月均187,804.40元);门店基础信息.营业面积(251㎡);租约汇总.租期结束(2026-09-25)</t>
+          <t>《2026H1门店经营台账.xlsx》Sheet「门店月度经营」的 `到店销售额`(2026H1 累计 811,660.23 元);《2026H1门店经营台账.xlsx》Sheet「门店费用」的 `租金及物业费`(月均 187,804.40 元);《2026H1门店经营台账.xlsx》Sheet「门店基础信息」的 `营业面积`(251 ㎡);《华东区门店租约汇总.docx》该门店的 `租期结束`(2026-09-25)与 `闭店条件`</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(2,083,298.29元);门店费用.租金及物业费(月均33,392.82元);门店基础信息.营业面积(126㎡)</t>
+          <t>《2026H1门店经营台账.xlsx》Sheet「门店月度经营」的 `到店销售额`(2026H1 累计 2,083,298.29 元);《2026H1门店经营台账.xlsx》Sheet「门店费用」的 `租金及物业费`(月均 33,392.82 元);《2026H1门店经营台账.xlsx》Sheet「门店基础信息」的 `营业面积`(126 ㎡)</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(1,078,094.56元);门店费用.租金及物业费(月均48,943.72元);门店基础信息.营业面积(64㎡)</t>
+          <t>《2026H1门店经营台账.xlsx》Sheet「门店月度经营」的 `到店销售额`(2026H1 累计 1,078,094.56 元);《2026H1门店经营台账.xlsx》Sheet「门店费用」的 `租金及物业费`(月均 48,943.72 元);《2026H1门店经营台账.xlsx》Sheet「门店基础信息」的 `营业面积`(64 ㎡)</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(1,703,269.89元);门店费用.租金及物业费(月均83,719.03元);门店基础信息.营业面积(135㎡)</t>
+          <t>《2026H1门店经营台账.xlsx》Sheet「门店月度经营」的 `到店销售额`(2026H1 累计 1,703,269.89 元);《2026H1门店经营台账.xlsx》Sheet「门店费用」的 `租金及物业费`(月均 83,719.03 元);《2026H1门店经营台账.xlsx》Sheet「门店基础信息」的 `营业面积`(135 ㎡)</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(2,126,380.20元);门店费用.租金及物业费(月均148,974.82元);门店基础信息.营业面积(198㎡);租约汇总.租期结束(2027-05-13)</t>
+          <t>《2026H1门店经营台账.xlsx》Sheet「门店月度经营」的 `到店销售额`(2026H1 累计 2,126,380.20 元);《2026H1门店经营台账.xlsx》Sheet「门店费用」的 `租金及物业费`(月均 148,974.82 元);《2026H1门店经营台账.xlsx》Sheet「门店基础信息」的 `营业面积`(198 ㎡);《华东区门店租约汇总.docx》该门店的 `租期结束`(2027-05-13)与 `闭店条件`</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -2762,7 +2762,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(800,557.76元);门店费用.租金及物业费(月均176,483.89元);门店基础信息.营业面积(231㎡);租约汇总.租期结束(2028-03-02)</t>
+          <t>《2026H1门店经营台账.xlsx》Sheet「门店月度经营」的 `到店销售额`(2026H1 累计 800,557.76 元);《2026H1门店经营台账.xlsx》Sheet「门店费用」的 `租金及物业费`(月均 176,483.89 元);《2026H1门店经营台账.xlsx》Sheet「门店基础信息」的 `营业面积`(231 ㎡);《华东区门店租约汇总.docx》该门店的 `租期结束`(2028-03-02)与 `闭店条件`</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(1,618,461.29元);门店费用.租金及物业费(月均15,115.03元);门店基础信息.营业面积(70㎡)</t>
+          <t>《2026H1门店经营台账.xlsx》Sheet「门店月度经营」的 `到店销售额`(2026H1 累计 1,618,461.29 元);《2026H1门店经营台账.xlsx》Sheet「门店费用」的 `租金及物业费`(月均 15,115.03 元);《2026H1门店经营台账.xlsx》Sheet「门店基础信息」的 `营业面积`(70 ㎡)</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(1,206,445.09元);门店费用.租金及物业费(月均59,815.72元);门店基础信息.营业面积(103㎡)</t>
+          <t>《2026H1门店经营台账.xlsx》Sheet「门店月度经营」的 `到店销售额`(2026H1 累计 1,206,445.09 元);《2026H1门店经营台账.xlsx》Sheet「门店费用」的 `租金及物业费`(月均 59,815.72 元);《2026H1门店经营台账.xlsx》Sheet「门店基础信息」的 `营业面积`(103 ㎡)</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(2,097,836.45元);门店费用.租金及物业费(月均76,754.54元);门店基础信息.营业面积(129㎡)</t>
+          <t>《2026H1门店经营台账.xlsx》Sheet「门店月度经营」的 `到店销售额`(2026H1 累计 2,097,836.45 元);《2026H1门店经营台账.xlsx》Sheet「门店费用」的 `租金及物业费`(月均 76,754.54 元);《2026H1门店经营台账.xlsx》Sheet「门店基础信息」的 `营业面积`(129 ㎡)</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(1,652,896.21元);门店费用.租金及物业费(月均33,283.71元);门店基础信息.营业面积(76㎡)</t>
+          <t>《2026H1门店经营台账.xlsx》Sheet「门店月度经营」的 `到店销售额`(2026H1 累计 1,652,896.21 元);《2026H1门店经营台账.xlsx》Sheet「门店费用」的 `租金及物业费`(月均 33,283.71 元);《2026H1门店经营台账.xlsx》Sheet「门店基础信息」的 `营业面积`(76 ㎡)</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(1,785,056.94元);门店费用.租金及物业费(月均45,354.29元);门店基础信息.营业面积(118㎡)</t>
+          <t>《2026H1门店经营台账.xlsx》Sheet「门店月度经营」的 `到店销售额`(2026H1 累计 1,785,056.94 元);《2026H1门店经营台账.xlsx》Sheet「门店费用」的 `租金及物业费`(月均 45,354.29 元);《2026H1门店经营台账.xlsx》Sheet「门店基础信息」的 `营业面积`(118 ㎡)</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(1,821,262.13元);门店费用.租金及物业费(月均17,926.01元);门店基础信息.营业面积(84㎡)</t>
+          <t>《2026H1门店经营台账.xlsx》Sheet「门店月度经营」的 `到店销售额`(2026H1 累计 1,821,262.13 元);《2026H1门店经营台账.xlsx》Sheet「门店费用」的 `租金及物业费`(月均 17,926.01 元);《2026H1门店经营台账.xlsx》Sheet「门店基础信息」的 `营业面积`(84 ㎡)</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -3231,7 +3231,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(3,468,905.55元);门店费用.租金及物业费(月均25,808.68元);门店基础信息.营业面积(111㎡)</t>
+          <t>《2026H1门店经营台账.xlsx》Sheet「门店月度经营」的 `到店销售额`(2026H1 累计 3,468,905.55 元);《2026H1门店经营台账.xlsx》Sheet「门店费用」的 `租金及物业费`(月均 25,808.68 元);《2026H1门店经营台账.xlsx》Sheet「门店基础信息」的 `营业面积`(111 ㎡)</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -3298,7 +3298,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>《2026H1门店经营台账.xlsx》门店月度经营.到店销售额(1,986,525.16元);门店费用.租金及物业费(月均51,003.03元);门店基础信息.营业面积(101㎡)</t>
+          <t>《2026H1门店经营台账.xlsx》Sheet「门店月度经营」的 `到店销售额`(2026H1 累计 1,986,525.16 元);《2026H1门店经营台账.xlsx》Sheet「门店费用」的 `租金及物业费`(月均 51,003.03 元);《2026H1门店经营台账.xlsx》Sheet「门店基础信息」的 `营业面积`(101 ㎡)</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">

--- a/output/门店分级与调整建议.xlsx
+++ b/output/门店分级与调整建议.xlsx
@@ -1288,7 +1288,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>《2026H1门店经营台账.xlsx》Sheet「门店月度经营」的 `到店销售额`(2026H1 累计 1,104,936.58 元);《2026H1门店经营台账.xlsx》Sheet「门店费用」的 `租金及物业费`(月均 69,605.38 元);《2026H1门店经营台账.xlsx》Sheet「门店基础信息」的 `营业面积`(93 ㎡);《华东区门店租约汇总.docx》该门店的 `租期结束`(2028-11-19)与 `闭店条件`</t>
+          <t>《2026H1门店经营台账.xlsx》Sheet「门店月度经营」的 `到店销售额`(2026H1 累计 1,104,936.58 元);《2026H1门店经营台账.xlsx》Sheet「门店费用」的 `租金及物业费`(月均 69,605.38 元);《2026H1门店经营台账.xlsx》Sheet「门店基础信息」的 `营业面积`(93 ㎡);《华东区门店租约汇总.docx》该门店的 `租期结束`(2028-11-19)与 `闭店条件`;逐月 `租售比`(由 Sheet「门店费用」的 `租金及物业费` ÷ Sheet「门店月度经营」的 `到店销售额` 计算)连续 &gt;35% 最长 3 个月</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>《2026H1门店经营台账.xlsx》Sheet「门店月度经营」的 `到店销售额`(2026H1 累计 794,338.79 元);《2026H1门店经营台账.xlsx》Sheet「门店费用」的 `租金及物业费`(月均 57,515.15 元);《2026H1门店经营台账.xlsx》Sheet「门店基础信息」的 `营业面积`(102 ㎡);《华东区门店租约汇总.docx》该门店的 `租期结束`(2026-11-17)与 `闭店条件`</t>
+          <t>《2026H1门店经营台账.xlsx》Sheet「门店月度经营」的 `到店销售额`(2026H1 累计 794,338.79 元);《2026H1门店经营台账.xlsx》Sheet「门店费用」的 `租金及物业费`(月均 57,515.15 元);《2026H1门店经营台账.xlsx》Sheet「门店基础信息」的 `营业面积`(102 ㎡);《华东区门店租约汇总.docx》该门店的 `租期结束`(2026-11-17)与 `闭店条件`;逐月 `租售比`(由 Sheet「门店费用」的 `租金及物业费` ÷ Sheet「门店月度经营」的 `到店销售额` 计算)连续 &gt;35% 最长 6 个月</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>《2026H1门店经营台账.xlsx》Sheet「门店月度经营」的 `到店销售额`(2026H1 累计 636,656.67 元);《2026H1门店经营台账.xlsx》Sheet「门店费用」的 `租金及物业费`(月均 68,755.97 元);《2026H1门店经营台账.xlsx》Sheet「门店基础信息」的 `营业面积`(129 ㎡);《华东区门店租约汇总.docx》该门店的 `租期结束`(2027-04-26)与 `闭店条件`</t>
+          <t>《2026H1门店经营台账.xlsx》Sheet「门店月度经营」的 `到店销售额`(2026H1 累计 636,656.67 元);《2026H1门店经营台账.xlsx》Sheet「门店费用」的 `租金及物业费`(月均 68,755.97 元);《2026H1门店经营台账.xlsx》Sheet「门店基础信息」的 `营业面积`(129 ㎡);《华东区门店租约汇总.docx》该门店的 `租期结束`(2027-04-26)与 `闭店条件`;逐月 `租售比`(由 Sheet「门店费用」的 `租金及物业费` ÷ Sheet「门店月度经营」的 `到店销售额` 计算)连续 &gt;35% 最长 6 个月</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>《2026H1门店经营台账.xlsx》Sheet「门店月度经营」的 `到店销售额`(2026H1 累计 2,126,302.43 元);《2026H1门店经营台账.xlsx》Sheet「门店费用」的 `租金及物业费`(月均 130,475.79 元);《2026H1门店经营台账.xlsx》Sheet「门店基础信息」的 `营业面积`(178 ㎡);《华东区门店租约汇总.docx》该门店的 `租期结束`(2032-11-25)与 `闭店条件`</t>
+          <t>《2026H1门店经营台账.xlsx》Sheet「门店月度经营」的 `到店销售额`(2026H1 累计 2,126,302.43 元);《2026H1门店经营台账.xlsx》Sheet「门店费用」的 `租金及物业费`(月均 130,475.79 元);《2026H1门店经营台账.xlsx》Sheet「门店基础信息」的 `营业面积`(178 ㎡);《华东区门店租约汇总.docx》该门店的 `租期结束`(2032-11-25)与 `闭店条件`;逐月 `租售比`(由 Sheet「门店费用」的 `租金及物业费` ÷ Sheet「门店月度经营」的 `到店销售额` 计算)连续 &gt;35% 最长 3 个月</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>《2026H1门店经营台账.xlsx》Sheet「门店月度经营」的 `到店销售额`(2026H1 累计 811,660.23 元);《2026H1门店经营台账.xlsx》Sheet「门店费用」的 `租金及物业费`(月均 187,804.40 元);《2026H1门店经营台账.xlsx》Sheet「门店基础信息」的 `营业面积`(251 ㎡);《华东区门店租约汇总.docx》该门店的 `租期结束`(2026-09-25)与 `闭店条件`</t>
+          <t>《2026H1门店经营台账.xlsx》Sheet「门店月度经营」的 `到店销售额`(2026H1 累计 811,660.23 元);《2026H1门店经营台账.xlsx》Sheet「门店费用」的 `租金及物业费`(月均 187,804.40 元);《2026H1门店经营台账.xlsx》Sheet「门店基础信息」的 `营业面积`(251 ㎡);《华东区门店租约汇总.docx》该门店的 `租期结束`(2026-09-25)与 `闭店条件`;逐月 `租售比`(由 Sheet「门店费用」的 `租金及物业费` ÷ Sheet「门店月度经营」的 `到店销售额` 计算)连续 &gt;35% 最长 6 个月</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -2690,12 +2690,12 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>转前置仓或自提点</t>
+          <t>整改</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>《2026H1门店经营台账.xlsx》Sheet「门店月度经营」的 `到店销售额`(2026H1 累计 2,126,380.20 元);《2026H1门店经营台账.xlsx》Sheet「门店费用」的 `租金及物业费`(月均 148,974.82 元);《2026H1门店经营台账.xlsx》Sheet「门店基础信息」的 `营业面积`(198 ㎡);《华东区门店租约汇总.docx》该门店的 `租期结束`(2027-05-13)与 `闭店条件`</t>
+          <t>《2026H1门店经营台账.xlsx》Sheet「门店月度经营」的 `到店销售额`(2026H1 累计 2,126,380.20 元);《2026H1门店经营台账.xlsx》Sheet「门店费用」的 `租金及物业费`(月均 148,974.82 元);《2026H1门店经营台账.xlsx》Sheet「门店基础信息」的 `营业面积`(198 ㎡);《华东区门店租约汇总.docx》该门店的 `租期结束`(2027-05-13)与 `闭店条件`;逐月 `租售比`(由 Sheet「门店费用」的 `租金及物业费` ÷ Sheet「门店月度经营」的 `到店销售额` 计算)连续 &gt;35% 最长 2 个月</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -2762,7 +2762,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>《2026H1门店经营台账.xlsx》Sheet「门店月度经营」的 `到店销售额`(2026H1 累计 800,557.76 元);《2026H1门店经营台账.xlsx》Sheet「门店费用」的 `租金及物业费`(月均 176,483.89 元);《2026H1门店经营台账.xlsx》Sheet「门店基础信息」的 `营业面积`(231 ㎡);《华东区门店租约汇总.docx》该门店的 `租期结束`(2028-03-02)与 `闭店条件`</t>
+          <t>《2026H1门店经营台账.xlsx》Sheet「门店月度经营」的 `到店销售额`(2026H1 累计 800,557.76 元);《2026H1门店经营台账.xlsx》Sheet「门店费用」的 `租金及物业费`(月均 176,483.89 元);《2026H1门店经营台账.xlsx》Sheet「门店基础信息」的 `营业面积`(231 ㎡);《华东区门店租约汇总.docx》该门店的 `租期结束`(2028-03-02)与 `闭店条件`;逐月 `租售比`(由 Sheet「门店费用」的 `租金及物业费` ÷ Sheet「门店月度经营」的 `到店销售额` 计算)连续 &gt;35% 最长 6 个月</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
